--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,19 +421,19 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>43132</v>
       </c>
       <c r="B2" t="n">
@@ -453,7 +441,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>43160</v>
       </c>
       <c r="B3" t="n">
@@ -461,7 +449,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>43191</v>
       </c>
       <c r="B4" t="n">
@@ -469,7 +457,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>43221</v>
       </c>
       <c r="B5" t="n">
@@ -477,7 +465,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>43252</v>
       </c>
       <c r="B6" t="n">
@@ -485,7 +473,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>43282</v>
       </c>
       <c r="B7" t="n">
@@ -493,7 +481,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>43313</v>
       </c>
       <c r="B8" t="n">
@@ -501,7 +489,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>43344</v>
       </c>
       <c r="B9" t="n">
@@ -509,7 +497,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>43374</v>
       </c>
       <c r="B10" t="n">
@@ -517,7 +505,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>43405</v>
       </c>
       <c r="B11" t="n">
@@ -525,7 +513,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="B12" t="n">
@@ -533,7 +521,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>43466</v>
       </c>
       <c r="B13" t="n">
@@ -541,7 +529,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>43497</v>
       </c>
       <c r="B14" t="n">
@@ -549,7 +537,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>43525</v>
       </c>
       <c r="B15" t="n">
@@ -557,7 +545,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>43556</v>
       </c>
       <c r="B16" t="n">
@@ -565,7 +553,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>43586</v>
       </c>
       <c r="B17" t="n">
@@ -573,7 +561,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>43617</v>
       </c>
       <c r="B18" t="n">
@@ -581,7 +569,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>43647</v>
       </c>
       <c r="B19" t="n">
@@ -589,7 +577,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>43678</v>
       </c>
       <c r="B20" t="n">
@@ -597,7 +585,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>43709</v>
       </c>
       <c r="B21" t="n">
@@ -605,7 +593,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>43739</v>
       </c>
       <c r="B22" t="n">
@@ -613,7 +601,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>43770</v>
       </c>
       <c r="B23" t="n">
@@ -621,7 +609,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="B24" t="n">
@@ -629,7 +617,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="B25" t="n">
@@ -637,7 +625,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>43862</v>
       </c>
       <c r="B26" t="n">
@@ -645,7 +633,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>43891</v>
       </c>
       <c r="B27" t="n">
@@ -653,7 +641,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>43922</v>
       </c>
       <c r="B28" t="n">
@@ -661,7 +649,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="B29" t="n">
@@ -669,7 +657,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>43983</v>
       </c>
       <c r="B30" t="n">
@@ -677,7 +665,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="B31" t="n">
@@ -685,7 +673,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="B32" t="n">
@@ -693,7 +681,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44075</v>
       </c>
       <c r="B33" t="n">
@@ -701,7 +689,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="B34" t="n">
@@ -709,7 +697,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>44136</v>
       </c>
       <c r="B35" t="n">
@@ -717,7 +705,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="B36" t="n">
@@ -725,7 +713,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>44197</v>
       </c>
       <c r="B37" t="n">
@@ -733,7 +721,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>44228</v>
       </c>
       <c r="B38" t="n">
@@ -741,7 +729,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>44256</v>
       </c>
       <c r="B39" t="n">
@@ -749,7 +737,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>44287</v>
       </c>
       <c r="B40" t="n">
@@ -757,7 +745,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>44317</v>
       </c>
       <c r="B41" t="n">
@@ -765,7 +753,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>44348</v>
       </c>
       <c r="B42" t="n">
@@ -773,7 +761,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>44378</v>
       </c>
       <c r="B43" t="n">
@@ -781,7 +769,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>44409</v>
       </c>
       <c r="B44" t="n">
@@ -789,7 +777,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>44440</v>
       </c>
       <c r="B45" t="n">
@@ -797,7 +785,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>44470</v>
       </c>
       <c r="B46" t="n">
@@ -805,7 +793,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>44501</v>
       </c>
       <c r="B47" t="n">
@@ -813,7 +801,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="B48" t="n">
@@ -821,7 +809,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>44562</v>
       </c>
       <c r="B49" t="n">
@@ -829,7 +817,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>44593</v>
       </c>
       <c r="B50" t="n">
@@ -837,7 +825,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>44621</v>
       </c>
       <c r="B51" t="n">
@@ -845,7 +833,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="B52" t="n">
@@ -853,7 +841,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="B53" t="n">
@@ -861,7 +849,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="B54" t="n">
@@ -869,7 +857,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="B55" t="n">
@@ -877,7 +865,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="B56" t="n">
@@ -885,7 +873,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="B57" t="n">
@@ -893,7 +881,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="B58" t="n">
@@ -901,7 +889,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="B59" t="n">
@@ -909,7 +897,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="B60" t="n">
@@ -917,7 +905,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="B61" t="n">
@@ -925,7 +913,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44958</v>
       </c>
       <c r="B62" t="n">
@@ -933,7 +921,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="B63" t="n">
@@ -941,7 +929,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>45017</v>
       </c>
       <c r="B64" t="n">
@@ -949,7 +937,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="B65" t="n">
@@ -957,7 +945,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="B66" t="n">
@@ -965,7 +953,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>45108</v>
       </c>
       <c r="B67" t="n">
@@ -973,7 +961,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="B68" t="n">
@@ -981,7 +969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="B69" t="n">
@@ -989,7 +977,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>45200</v>
       </c>
       <c r="B70" t="n">
@@ -997,7 +985,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="B71" t="n">
@@ -1005,7 +993,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="B72" t="n">
@@ -1013,7 +1001,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>45292</v>
       </c>
       <c r="B73" t="n">
@@ -1021,7 +1009,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="B74" t="n">
@@ -1029,7 +1017,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="B75" t="n">
@@ -1037,7 +1025,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="B76" t="n">
@@ -1045,7 +1033,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="B77" t="n">
@@ -1053,7 +1041,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>45444</v>
       </c>
       <c r="B78" t="n">
@@ -1061,7 +1049,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="B79" t="n">
@@ -1069,7 +1057,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="B80" t="n">
@@ -1077,7 +1065,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="B81" t="n">
@@ -1085,7 +1073,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="B82" t="n">
@@ -1093,7 +1081,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>45597</v>
       </c>
       <c r="B83" t="n">
@@ -1101,7 +1089,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="B84" t="n">
@@ -1109,7 +1097,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>45658</v>
       </c>
       <c r="B85" t="n">
@@ -1117,7 +1105,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="B86" t="n">
@@ -1125,7 +1113,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>45717</v>
       </c>
       <c r="B87" t="n">
@@ -1133,7 +1121,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>45748</v>
       </c>
       <c r="B88" t="n">
@@ -1141,7 +1129,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>45778</v>
       </c>
       <c r="B89" t="n">
@@ -1149,7 +1137,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>45809</v>
       </c>
       <c r="B90" t="n">
@@ -1157,7 +1145,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>45839</v>
       </c>
       <c r="B91" t="n">
@@ -1165,7 +1153,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>45870</v>
       </c>
       <c r="B92" t="n">
@@ -1173,7 +1161,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>45901</v>
       </c>
       <c r="B93" t="n">
@@ -1181,7 +1169,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="B94" t="n">
@@ -1189,7 +1177,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>45962</v>
       </c>
       <c r="B95" t="n">
@@ -1197,7 +1185,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="B96" t="n">
@@ -1205,7 +1193,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>46023</v>
       </c>
       <c r="B97" t="n">

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,6 +1200,14 @@
         <v>3.94</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B98" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,14 @@
         <v>3.92</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B99" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,6 +1216,14 @@
         <v>3.75</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1224,14 @@
         <v>3.74</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B101" t="n">
+        <v>3.78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,14 @@
         <v>3.78</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B102" t="n">
+        <v>3.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,14 @@
         <v>3.95</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B103" t="n">
+        <v>4.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/update/historicos/expectativas_inflacion_mexico.xlsx
+++ b/update/historicos/expectativas_inflacion_mexico.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,14 @@
         <v>4.18</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B104" t="n">
+        <v>4.13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
